--- a/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
@@ -539,10 +539,10 @@
         <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="H10" t="n">
-        <v>0.88</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.64</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="14">
@@ -750,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>15.76</v>
+        <v>15.48</v>
       </c>
       <c r="H22" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>15.92</v>
+        <v>15.63</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
@@ -565,10 +565,10 @@
         <v>0.14</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>1.96</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="12">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.36</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="14">
@@ -750,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>15.48</v>
+        <v>20.24</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>15.63</v>
+        <v>20.44</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 17 Equipamiento y mobiliario fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Mesones y topes</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-02-040.xlsx
@@ -478,14 +478,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Tope o encimera de área de lavado.</t>
+          <t>Tope o mesón de área de lavado.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de tope o encimera en el área de lavado o de servicio, con su recorte para el lavadero y su canto trabajado. Incluye la plantilla en obra sobre la base ya nivelada, el mecanizado del recorte, el presentado y nivelado, el sellado del canto de corte que es por donde el material absorbe humedad en un área permanentemente mojada, la fijación y el sellado perimetral contra la pared. El material lo elige el cliente y se presupuesta aparte. Medido en longitud de tope.
+          <t xml:space="preserve">Suministro e instalación de tope o mesón en el área de lavado o de servicio, con su recorte para el lavadero y su canto trabajado. Incluye la plantilla en obra sobre la base ya nivelada, el mecanizado del recorte, el presentado y nivelado, el sellado del canto de corte que es por donde el material absorbe humedad en un área permanentemente mojada, la fijación y el sellado perimetral contra la pared. El material lo elige el cliente y se presupuesta aparte. Medido en longitud de tope.
 </t>
         </is>
       </c>
@@ -680,7 +680,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F18" t="n">
